--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -102,10 +102,10 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>34105-7</t>
-  </si>
-  <si>
-    <t>Hospital Discharge summary</t>
+    <t>18842-5</t>
+  </si>
+  <si>
+    <t>Discharge summary</t>
   </si>
   <si>
     <t/>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/resq-stroke-discharge-document-type-vs</t>
+    <t>http://qualityregistry.org/ValueSet/resq-stroke-discharge-document-type-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed document type code for the RESQ Stroke Hospital Discharge Summary Composition.</t>
+    <t>Allowed document type code for the RESQ Stroke Discharge Patient Summary Composition.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-document-type-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
